--- a/outputs/48975.xlsx
+++ b/outputs/48975.xlsx
@@ -340,115 +340,115 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F33" s="15"/>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
@@ -1250,7 +1250,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="47.66"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="19"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -1270,21 +1270,21 @@
         <v>Header</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="22"/>
       <c r="B4" s="24" t="str">
         <f aca="false">Input!B4</f>
         <v>Header</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="20"/>
       <c r="B5" s="25"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26"/>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1303,7 +1303,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="28" t="str">
-        <f aca="false" t="array" ref="B11:B17">INDEX(Input!B9:B33,SMALL(IF(Input!E9:E33="yes",ROW(Input!E9:E33)-8),ROW()-10))</f>
+        <f aca="false">Input!B9</f>
         <v>Text 1</v>
       </c>
     </row>
@@ -1313,6 +1313,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="28" t="str">
+        <f aca="false">Input!B10</f>
         <v>Text 2</v>
       </c>
     </row>
@@ -1322,6 +1323,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="28" t="str">
+        <f aca="false">Input!B11</f>
         <v>Text 3</v>
       </c>
     </row>
@@ -1331,6 +1333,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="28" t="str">
+        <f aca="false">Input!B12</f>
         <v>Text 4</v>
       </c>
     </row>
@@ -1340,6 +1343,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="28" t="str">
+        <f aca="false">Input!B18</f>
         <v>Text 10</v>
       </c>
     </row>
@@ -1349,6 +1353,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="28" t="str">
+        <f aca="false">Input!B23</f>
         <v>Text 15</v>
       </c>
     </row>
@@ -1358,6 +1363,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="28" t="str">
+        <f aca="false">Input!B33</f>
         <v>Text 25</v>
       </c>
     </row>
